--- a/data/trending_integrated_20261021_13.xlsx
+++ b/data/trending_integrated_20261021_13.xlsx
@@ -610,7 +610,7 @@
         <v>0.79</v>
       </c>
       <c r="O2" t="n">
-        <v>10577517757</v>
+        <v>10579840257</v>
       </c>
       <c r="P2" t="n">
         <v>2665</v>
@@ -619,7 +619,7 @@
         <v>292</v>
       </c>
       <c r="R2" t="n">
-        <v>-114000</v>
+        <v>-105000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14820</v>
+        <v>14810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+22.68%</t>
+          <t>'+22.60%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.27</v>
       </c>
       <c r="E3" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F3" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G3" t="n">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0.27</v>
       </c>
       <c r="O3" t="n">
-        <v>91822611290</v>
+        <v>92440212845</v>
       </c>
       <c r="P3" t="n">
         <v>28800</v>
@@ -711,10 +711,10 @@
         <v>12030</v>
       </c>
       <c r="R3" t="n">
-        <v>139000</v>
+        <v>162000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1820</v>
+        <v>1841</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+19.74%</t>
+          <t>'+21.12%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.12</v>
       </c>
       <c r="E4" t="n">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="F4" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="G4" t="n">
-        <v>263</v>
+        <v>286</v>
       </c>
       <c r="H4" t="n">
         <v>0.6899999999999999</v>
@@ -794,7 +794,7 @@
         <v>0.57</v>
       </c>
       <c r="O4" t="n">
-        <v>52980465231</v>
+        <v>57163262905</v>
       </c>
       <c r="P4" t="n">
         <v>3980</v>
@@ -803,23 +803,23 @@
         <v>1115</v>
       </c>
       <c r="R4" t="n">
-        <v>393000</v>
+        <v>-148000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>푸드나무 경영권 인수 (주당 3500원) 및 3연상 기대감 고조. 랭킹닭컴 관련 사업 성장 전망.</t>
+          <t>그린하버의 경영권 인수 확정. 2연속 하한가 이후 반등 및 3연상 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['인수', '랭킹닭컴', '3연상']</t>
+          <t>['인수', '경영권', '하한가']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11130</v>
+        <v>11160</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.92%</t>
+          <t>'+14.23%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>161</v>
       </c>
       <c r="F5" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G5" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H5" t="n">
         <v>1.28</v>
@@ -886,7 +886,7 @@
         <v>0.88</v>
       </c>
       <c r="O5" t="n">
-        <v>260992644700</v>
+        <v>265202496825</v>
       </c>
       <c r="P5" t="n">
         <v>11690</v>
@@ -895,14 +895,14 @@
         <v>2270</v>
       </c>
       <c r="R5" t="n">
-        <v>350000</v>
+        <v>-13000</v>
       </c>
       <c r="S5" t="n">
-        <v>-16000</v>
+        <v>-98000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>인공지능 데이터센터 수주 잔고 1조원 돌파 전망. 로봇주 테마와 함께 신고가 경신 기대.</t>
+          <t>로봇 및 AI 데이터센터 관련 수혜 기대감. 높은 수주잔고 대비 저평가.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['수주잔고', '데이터센터', '로봇주']</t>
+          <t>['로봇', 'AI', '수주잔고']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9270</v>
+        <v>9320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.17%</t>
+          <t>'+7.75%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.66</v>
       </c>
       <c r="E6" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F6" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G6" t="n">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="H6" t="n">
         <v>5.34</v>
@@ -978,7 +978,7 @@
         <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>28477282085</v>
+        <v>28926058495</v>
       </c>
       <c r="P6" t="n">
         <v>14940</v>
@@ -987,14 +987,14 @@
         <v>5390</v>
       </c>
       <c r="R6" t="n">
-        <v>225000</v>
+        <v>257000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>테슬라 관련 긍정적 뉴스 및 실적 전망에 힘입어 거래량이 증가하며 주가 상승에 대한 기대감이 반영됨.</t>
+          <t>테슬라 관련주로 부각되며 상승 기대감. 높은 영업이익 대비 낮은 시가총액.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['테슬라', '영업이익', '주가상승']</t>
+          <t>['테슬라', '영업이익', '시가총액']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>221250</v>
+        <v>220750</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.61%</t>
+          <t>'+4.37%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="G7" t="n">
-        <v>1886</v>
+        <v>1772</v>
       </c>
       <c r="H7" t="n">
         <v>46.08</v>
@@ -1070,7 +1070,7 @@
         <v>46.04</v>
       </c>
       <c r="O7" t="n">
-        <v>2370920268500</v>
+        <v>2466032882500</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1079,23 +1079,23 @@
         <v>94500</v>
       </c>
       <c r="R7" t="n">
-        <v>1981000</v>
+        <v>2729000</v>
       </c>
       <c r="S7" t="n">
-        <v>380000</v>
+        <v>497000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>외인 기관 동반 매수세 유입 및 222,000원 하방 지지 확인. 반도체 관련 악재 속에서도 긍정적 흐름 기대.</t>
+          <t>외국인 및 기관 동반 매수세 유입에 따른 반등 기대. 반도체 관련 지정학적 이슈.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['외인', '기관', '지지']</t>
+          <t>['반도체', '외인', '기관']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1273000</v>
+        <v>14730</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.09%</t>
+          <t>'+4.03%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>107</v>
       </c>
       <c r="F8" t="n">
-        <v>476</v>
+        <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>1763</v>
+        <v>234</v>
       </c>
       <c r="H8" t="n">
-        <v>48.77</v>
+        <v>9.82</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,47 +1147,47 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1223000</v>
+        <v>14160</v>
       </c>
       <c r="K8" t="n">
-        <v>1260000</v>
+        <v>14340</v>
       </c>
       <c r="L8" t="n">
-        <v>1329000</v>
+        <v>14830</v>
       </c>
       <c r="M8" t="n">
-        <v>1258000</v>
+        <v>14340</v>
       </c>
       <c r="N8" t="n">
-        <v>48.81</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>3373808861000</v>
+        <v>25819331530</v>
       </c>
       <c r="P8" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q8" t="n">
-        <v>468000</v>
+        <v>3320</v>
       </c>
       <c r="R8" t="n">
-        <v>150000</v>
+        <v>353000</v>
       </c>
       <c r="S8" t="n">
-        <v>73000</v>
+        <v>14000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>자사주 매입 및 소각을 통한 주가 방어 시도. 마이크론 파업 및 솔리다임 상장 이슈 반영.</t>
+          <t>외국인, 연기금 순매수 유입 및 텐베거 가능성 언급. 이재명 관련 정치적 언급 다수.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['자사주', '솔리다임', '주가 방어']</t>
+          <t>['외인', '연기금', '텐베거']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14730</v>
+        <v>1266000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.03%</t>
+          <t>'+3.52%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="E9" t="n">
-        <v>105</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>44</v>
+        <v>479</v>
       </c>
       <c r="G9" t="n">
-        <v>231</v>
+        <v>1709</v>
       </c>
       <c r="H9" t="n">
-        <v>9.82</v>
+        <v>48.77</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,47 +1239,47 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14160</v>
+        <v>1223000</v>
       </c>
       <c r="K9" t="n">
-        <v>14340</v>
+        <v>1260000</v>
       </c>
       <c r="L9" t="n">
-        <v>14830</v>
+        <v>1329000</v>
       </c>
       <c r="M9" t="n">
-        <v>14340</v>
+        <v>1258000</v>
       </c>
       <c r="N9" t="n">
-        <v>9.779999999999999</v>
+        <v>48.81</v>
       </c>
       <c r="O9" t="n">
-        <v>25286466660</v>
+        <v>3508209295500</v>
       </c>
       <c r="P9" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q9" t="n">
-        <v>3320</v>
+        <v>468000</v>
       </c>
       <c r="R9" t="n">
-        <v>133000</v>
+        <v>309000</v>
       </c>
       <c r="S9" t="n">
-        <v>9000</v>
+        <v>57000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>외국인, 연기금 순매수 유입 및 텐베거 가능성 언급. 이재명 관련 정치적 언급 다수.</t>
+          <t>자사주 매입에 따른 단기 반등 가능성. 마이크론 파업 관련 이슈.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['외인', '연기금', '텐베거']</t>
+          <t>['자사주', '마이크론', '반등']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2925</v>
+        <v>2920</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.99%</t>
+          <t>'+2.82%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>32</v>
       </c>
       <c r="G10" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H10" t="n">
         <v>5.82</v>
@@ -1346,7 +1346,7 @@
         <v>5.91</v>
       </c>
       <c r="O10" t="n">
-        <v>16468842779</v>
+        <v>16532255924</v>
       </c>
       <c r="P10" t="n">
         <v>19950</v>
@@ -1355,7 +1355,7 @@
         <v>1913</v>
       </c>
       <c r="R10" t="n">
-        <v>-1200000</v>
+        <v>-1060000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1395,18 +1395,18 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17670</v>
+        <v>17740</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.02%</t>
+          <t>'+2.42%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F11" t="n">
         <v>53</v>
@@ -1438,7 +1438,7 @@
         <v>27.78</v>
       </c>
       <c r="O11" t="n">
-        <v>31934606525</v>
+        <v>33323828080</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1447,10 +1447,10 @@
         <v>17170</v>
       </c>
       <c r="R11" t="n">
-        <v>146000</v>
+        <v>477000</v>
       </c>
       <c r="S11" t="n">
-        <v>24000</v>
+        <v>13000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7390</v>
+        <v>63950</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.65%</t>
+          <t>'+1.83%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="F12" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="G12" t="n">
-        <v>292</v>
+        <v>469</v>
       </c>
       <c r="H12" t="n">
-        <v>25.45</v>
+        <v>22.23</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>7270</v>
+        <v>62800</v>
       </c>
       <c r="K12" t="n">
-        <v>7360</v>
+        <v>63600</v>
       </c>
       <c r="L12" t="n">
-        <v>7520</v>
+        <v>64800</v>
       </c>
       <c r="M12" t="n">
-        <v>7250</v>
+        <v>62600</v>
       </c>
       <c r="N12" t="n">
-        <v>25.4</v>
+        <v>22.29</v>
       </c>
       <c r="O12" t="n">
-        <v>11096014400</v>
+        <v>65881825050</v>
       </c>
       <c r="P12" t="n">
-        <v>17950</v>
+        <v>139200</v>
       </c>
       <c r="Q12" t="n">
-        <v>7190</v>
+        <v>57000</v>
       </c>
       <c r="R12" t="n">
-        <v>131000</v>
+        <v>-57000</v>
       </c>
       <c r="S12" t="n">
-        <v>-2000</v>
+        <v>25000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>높은 신용 비율과 부채로 인한 불안감 형성. 외국인 프로그램 매수세 유입 및 실적 개선 기대.</t>
+          <t>원전 및 전력 관련주로 분류되나, 주가 부진 지속. 외국인 매도세 관찰.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['신용', '부채', '프로그램매수']</t>
+          <t>['원전', '전력', '외국인']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>63800</v>
+        <v>1585</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.59%</t>
+          <t>'+0.76%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.06</v>
+        <v>-0.93</v>
       </c>
       <c r="E13" t="n">
-        <v>148</v>
+        <v>80</v>
       </c>
       <c r="F13" t="n">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="G13" t="n">
-        <v>474</v>
+        <v>229</v>
       </c>
       <c r="H13" t="n">
-        <v>22.23</v>
+        <v>0.84</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>62800</v>
+        <v>1573</v>
       </c>
       <c r="K13" t="n">
-        <v>63600</v>
+        <v>1650</v>
       </c>
       <c r="L13" t="n">
-        <v>64800</v>
+        <v>1715</v>
       </c>
       <c r="M13" t="n">
-        <v>62600</v>
+        <v>1573</v>
       </c>
       <c r="N13" t="n">
-        <v>22.29</v>
+        <v>1.77</v>
       </c>
       <c r="O13" t="n">
-        <v>64701977000</v>
+        <v>29045178818</v>
       </c>
       <c r="P13" t="n">
-        <v>139200</v>
+        <v>2970</v>
       </c>
       <c r="Q13" t="n">
-        <v>57000</v>
+        <v>890</v>
       </c>
       <c r="R13" t="n">
-        <v>-40000</v>
+        <v>-797000</v>
       </c>
       <c r="S13" t="n">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>국내 주식 시장의 변동성 속에서 원전, 전력 관련 수혜 기대. 공매도 금지 및 정부 정책 언급.</t>
+          <t>스페이스X 관련 시간 외 급등 및 기술력 보유로 인한 기대감. 수주 계약 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['원전', '전력', '공매도']</t>
+          <t>['스페이스X', '기술력', '수혜주']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1592</v>
+        <v>7380</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+1.21%</t>
+          <t>'-1.86%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.93</v>
+        <v>0.05</v>
       </c>
       <c r="E14" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F14" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="G14" t="n">
-        <v>226</v>
+        <v>305</v>
       </c>
       <c r="H14" t="n">
-        <v>0.84</v>
+        <v>25.45</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,60 +1699,60 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1573</v>
+        <v>7520</v>
       </c>
       <c r="K14" t="n">
-        <v>1650</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1715</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1573</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.77</v>
+        <v>25.4</v>
       </c>
       <c r="O14" t="n">
-        <v>28891869402</v>
+        <v>11392000000</v>
       </c>
       <c r="P14" t="n">
-        <v>2970</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>890</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>-746000</v>
+        <v>268000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>스페이스X 수혜 기대감 속 거래량 증가. 단기 급등 가능성 있으나 윗꼬리 부담.</t>
+          <t>실적 부진 및 유상증자 가능성에 대한 우려. 프로그램 환매수 관찰.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['스페이스X', '수혜주', '거래량']</t>
+          <t>['실적', '유상증자', '환매수']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3112</v>
+        <v>3100</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.80%</t>
+          <t>'-4.17%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.73</v>
       </c>
       <c r="E15" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F15" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G15" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1806,7 +1806,7 @@
         <v>0.73</v>
       </c>
       <c r="O15" t="n">
-        <v>10110889555</v>
+        <v>10292441460</v>
       </c>
       <c r="P15" t="n">
         <v>7050</v>
@@ -1815,7 +1815,7 @@
         <v>2500</v>
       </c>
       <c r="R15" t="n">
-        <v>-103000</v>
+        <v>-129000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4282</v>
+        <v>4265</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-7.52%</t>
+          <t>'-7.88%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F16" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G16" t="n">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="H16" t="n">
         <v>8.58</v>
@@ -1898,7 +1898,7 @@
         <v>8.57</v>
       </c>
       <c r="O16" t="n">
-        <v>20900622322</v>
+        <v>21231509434</v>
       </c>
       <c r="P16" t="n">
         <v>7560</v>
@@ -1907,10 +1907,10 @@
         <v>2930</v>
       </c>
       <c r="R16" t="n">
-        <v>-1027000</v>
+        <v>-1377000</v>
       </c>
       <c r="S16" t="n">
-        <v>-162000</v>
+        <v>-462000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>

--- a/data/trending_integrated_20261021_13.xlsx
+++ b/data/trending_integrated_20261021_13.xlsx
@@ -578,13 +578,13 @@
         <v>3.15</v>
       </c>
       <c r="E2" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G2" t="n">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="H2" t="n">
         <v>3.94</v>
@@ -610,7 +610,7 @@
         <v>0.79</v>
       </c>
       <c r="O2" t="n">
-        <v>10579840257</v>
+        <v>10584400257</v>
       </c>
       <c r="P2" t="n">
         <v>2665</v>
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14810</v>
+        <v>14850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+22.60%</t>
+          <t>'+22.93%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -673,10 +673,10 @@
         <v>66</v>
       </c>
       <c r="F3" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G3" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0.27</v>
       </c>
       <c r="O3" t="n">
-        <v>92440212845</v>
+        <v>92803032565</v>
       </c>
       <c r="P3" t="n">
         <v>28800</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1841</v>
+        <v>1828</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+21.12%</t>
+          <t>'+20.26%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.12</v>
       </c>
       <c r="E4" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F4" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G4" t="n">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="H4" t="n">
         <v>0.6899999999999999</v>
@@ -794,7 +794,7 @@
         <v>0.57</v>
       </c>
       <c r="O4" t="n">
-        <v>57163262905</v>
+        <v>58977454720</v>
       </c>
       <c r="P4" t="n">
         <v>3980</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>그린하버의 경영권 인수 확정. 2연속 하한가 이후 반등 및 3연상 기대감.</t>
+          <t>그린하버의 경영권 인수 결정으로 인한 급등세. 355억 규모의 인수 발표와 역대급 거래량 터진 손바뀜에 대한 긍정적 전망. 인수설이 사실로 확인되며 급등.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['인수', '경영권', '하한가']</t>
+          <t>['인수', '경영권', '손바뀜']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11160</v>
+        <v>11110</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+14.23%</t>
+          <t>'+13.72%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.4</v>
       </c>
       <c r="E5" t="n">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="F5" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G5" t="n">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="H5" t="n">
         <v>1.28</v>
@@ -886,7 +886,7 @@
         <v>0.88</v>
       </c>
       <c r="O5" t="n">
-        <v>265202496825</v>
+        <v>268191049045</v>
       </c>
       <c r="P5" t="n">
         <v>11690</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9320</v>
+        <v>9280</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.75%</t>
+          <t>'+7.28%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.66</v>
       </c>
       <c r="E6" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F6" t="n">
         <v>62</v>
       </c>
       <c r="G6" t="n">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="H6" t="n">
         <v>5.34</v>
@@ -978,7 +978,7 @@
         <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>28926058495</v>
+        <v>29064706615</v>
       </c>
       <c r="P6" t="n">
         <v>14940</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>테슬라 관련주로 부각되며 상승 기대감. 높은 영업이익 대비 낮은 시가총액.</t>
+          <t>나스닥 상장 철회 가능성 언급 및 테슬라 관련 긍정적 뉴스에 대한 기대감. 그러나 주가 상승 시 찔끔 오르는 모습과 개미 털기에 대한 부정적인 의견 존재.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['테슬라', '영업이익', '시가총액']</t>
+          <t>['나스닥', '테슬라', '거래량']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>220750</v>
+        <v>14810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.37%</t>
+          <t>'+4.59%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>110</v>
       </c>
       <c r="F7" t="n">
-        <v>504</v>
+        <v>44</v>
       </c>
       <c r="G7" t="n">
-        <v>1772</v>
+        <v>239</v>
       </c>
       <c r="H7" t="n">
-        <v>46.08</v>
+        <v>9.82</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>211500</v>
+        <v>14160</v>
       </c>
       <c r="K7" t="n">
-        <v>217000</v>
+        <v>14340</v>
       </c>
       <c r="L7" t="n">
-        <v>228000</v>
+        <v>14830</v>
       </c>
       <c r="M7" t="n">
-        <v>217000</v>
+        <v>14340</v>
       </c>
       <c r="N7" t="n">
-        <v>46.04</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>2466032882500</v>
+        <v>26321431185</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q7" t="n">
-        <v>94500</v>
+        <v>3320</v>
       </c>
       <c r="R7" t="n">
-        <v>2729000</v>
+        <v>356000</v>
       </c>
       <c r="S7" t="n">
-        <v>497000</v>
+        <v>14000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>외국인 및 기관 동반 매수세 유입에 따른 반등 기대. 반도체 관련 지정학적 이슈.</t>
+          <t>이재명 대통령 관련 언급과 함께 주가 조작 의혹 제기. 외인 보유율 유지 및 대차 해지 중요성 언급. 일부 긍정적 전망도 있으나, 전반적으로 부정적 여론 존재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['반도체', '외인', '기관']</t>
+          <t>['주가조작', '외인보유율', '대차']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14730</v>
+        <v>221000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.03%</t>
+          <t>'+4.49%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>107</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>44</v>
+        <v>511</v>
       </c>
       <c r="G8" t="n">
-        <v>234</v>
+        <v>1780</v>
       </c>
       <c r="H8" t="n">
-        <v>9.82</v>
+        <v>46.08</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,47 +1147,47 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14160</v>
+        <v>211500</v>
       </c>
       <c r="K8" t="n">
-        <v>14340</v>
+        <v>217000</v>
       </c>
       <c r="L8" t="n">
-        <v>14830</v>
+        <v>228000</v>
       </c>
       <c r="M8" t="n">
-        <v>14340</v>
+        <v>217000</v>
       </c>
       <c r="N8" t="n">
-        <v>9.779999999999999</v>
+        <v>46.04</v>
       </c>
       <c r="O8" t="n">
-        <v>25819331530</v>
+        <v>2531679946000</v>
       </c>
       <c r="P8" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>3320</v>
+        <v>94500</v>
       </c>
       <c r="R8" t="n">
-        <v>353000</v>
+        <v>2736000</v>
       </c>
       <c r="S8" t="n">
-        <v>14000</v>
+        <v>497000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>외국인, 연기금 순매수 유입 및 텐베거 가능성 언급. 이재명 관련 정치적 언급 다수.</t>
+          <t>미국 중국 반도체 퇴출 결정, 외인 및 기관 동반 매수세 유입으로 인한 긍정적 전망. 그러나 개인 투자자들의 부정적 언급과 종가 음봉 마감에 대한 우려 존재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['외인', '연기금', '텐베거']</t>
+          <t>['반도체', '외인수급', '기관매수']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,191 +1200,191 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>아주IB투자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1266000</v>
+        <v>2925</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.52%</t>
+          <t>'+2.99%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.04</v>
+        <v>-0.09</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>76</v>
       </c>
       <c r="F9" t="n">
-        <v>479</v>
+        <v>33</v>
       </c>
       <c r="G9" t="n">
-        <v>1709</v>
+        <v>231</v>
       </c>
       <c r="H9" t="n">
-        <v>48.77</v>
+        <v>5.82</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1223000</v>
+        <v>2840</v>
       </c>
       <c r="K9" t="n">
-        <v>1260000</v>
+        <v>3100</v>
       </c>
       <c r="L9" t="n">
-        <v>1329000</v>
+        <v>3300</v>
       </c>
       <c r="M9" t="n">
-        <v>1258000</v>
+        <v>2855</v>
       </c>
       <c r="N9" t="n">
-        <v>48.81</v>
+        <v>5.91</v>
       </c>
       <c r="O9" t="n">
-        <v>3508209295500</v>
+        <v>16681612989</v>
       </c>
       <c r="P9" t="n">
-        <v>2987000</v>
+        <v>19950</v>
       </c>
       <c r="Q9" t="n">
-        <v>468000</v>
+        <v>1913</v>
       </c>
       <c r="R9" t="n">
-        <v>309000</v>
+        <v>-1060000</v>
       </c>
       <c r="S9" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>자사주 매입에 따른 단기 반등 가능성. 마이크론 파업 관련 이슈.</t>
+          <t>우주 섹터 관련 언급과 함께 주가 조작 의혹 제기. 반등 기대와 함께 신고 주장.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['자사주', '마이크론', '반등']</t>
+          <t>['우주섹터', '주가조작', '투자기업']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>027360</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>아주IB투자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2920</v>
+        <v>1259000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.82%</t>
+          <t>'+2.94%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.09</v>
+        <v>-0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>74</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>32</v>
+        <v>481</v>
       </c>
       <c r="G10" t="n">
-        <v>231</v>
+        <v>1506</v>
       </c>
       <c r="H10" t="n">
-        <v>5.82</v>
+        <v>48.77</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>2840</v>
+        <v>1223000</v>
       </c>
       <c r="K10" t="n">
-        <v>3100</v>
+        <v>1260000</v>
       </c>
       <c r="L10" t="n">
-        <v>3300</v>
+        <v>1329000</v>
       </c>
       <c r="M10" t="n">
-        <v>2855</v>
+        <v>1254000</v>
       </c>
       <c r="N10" t="n">
-        <v>5.91</v>
+        <v>48.81</v>
       </c>
       <c r="O10" t="n">
-        <v>16532255924</v>
+        <v>3641889056000</v>
       </c>
       <c r="P10" t="n">
-        <v>19950</v>
+        <v>2987000</v>
       </c>
       <c r="Q10" t="n">
-        <v>1913</v>
+        <v>468000</v>
       </c>
       <c r="R10" t="n">
-        <v>-1060000</v>
+        <v>326000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>우주 섹터 관련 언급과 함께 주가 조작 의혹 제기. 반등 기대와 함께 신고 주장.</t>
+          <t>개인 매도세와 연기금의 매도에 대한 부정적인 언급. 솔리다임 상장 관련 언급과 함께 주가 하락에 대한 불만 표출. 반등 시 기대감은 낮음.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['우주섹터', '주가조작', '투자기업']</t>
+          <t>['연기금', '개인매도', '솔리다임']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>027360</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17740</v>
+        <v>17820</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.42%</t>
+          <t>'+2.89%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F11" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G11" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="H11" t="n">
         <v>27.78</v>
@@ -1429,7 +1429,7 @@
         <v>17480</v>
       </c>
       <c r="L11" t="n">
-        <v>17820</v>
+        <v>17830</v>
       </c>
       <c r="M11" t="n">
         <v>17170</v>
@@ -1438,7 +1438,7 @@
         <v>27.78</v>
       </c>
       <c r="O11" t="n">
-        <v>33323828080</v>
+        <v>35105208915</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1447,23 +1447,23 @@
         <v>17170</v>
       </c>
       <c r="R11" t="n">
-        <v>477000</v>
+        <v>488000</v>
       </c>
       <c r="S11" t="n">
         <v>13000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>현 주가에 대한 부정적 전망과 함께 정치적 이슈가 언급되며 투자 심리가 위축됨.</t>
+          <t>조선, 방산, 원전 섹터 전반의 약세 속에서 주가 하락에 대한 부정적인 전망. 블랙록 매수 평균 단가 언급 등 일부 긍정적 요인도 있으나, 전반적으로 하락세 지속 우려.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['최저가', '떡락', '정치이슈']</t>
+          <t>['조선', '방산', '원전']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>63950</v>
+        <v>64100</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.83%</t>
+          <t>'+2.07%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F12" t="n">
         <v>85</v>
       </c>
       <c r="G12" t="n">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="H12" t="n">
         <v>22.23</v>
@@ -1530,7 +1530,7 @@
         <v>22.29</v>
       </c>
       <c r="O12" t="n">
-        <v>65881825050</v>
+        <v>68070195400</v>
       </c>
       <c r="P12" t="n">
         <v>139200</v>
@@ -1539,7 +1539,7 @@
         <v>57000</v>
       </c>
       <c r="R12" t="n">
-        <v>-57000</v>
+        <v>-59000</v>
       </c>
       <c r="S12" t="n">
         <v>25000</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1585</v>
+        <v>7400</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.76%</t>
+          <t>'+1.79%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.93</v>
+        <v>0.05</v>
       </c>
       <c r="E13" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F13" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G13" t="n">
-        <v>229</v>
+        <v>313</v>
       </c>
       <c r="H13" t="n">
-        <v>0.84</v>
+        <v>25.45</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1573</v>
+        <v>7270</v>
       </c>
       <c r="K13" t="n">
-        <v>1650</v>
+        <v>7360</v>
       </c>
       <c r="L13" t="n">
-        <v>1715</v>
+        <v>7520</v>
       </c>
       <c r="M13" t="n">
-        <v>1573</v>
+        <v>7250</v>
       </c>
       <c r="N13" t="n">
-        <v>1.77</v>
+        <v>25.4</v>
       </c>
       <c r="O13" t="n">
-        <v>29045178818</v>
+        <v>11557760940</v>
       </c>
       <c r="P13" t="n">
-        <v>2970</v>
+        <v>17950</v>
       </c>
       <c r="Q13" t="n">
-        <v>890</v>
+        <v>7190</v>
       </c>
       <c r="R13" t="n">
-        <v>-797000</v>
+        <v>268000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>스페이스X 관련 시간 외 급등 및 기술력 보유로 인한 기대감. 수주 계약 기대.</t>
+          <t>3분기 실적 흑자 전환 기대감 및 외인 프로그램 환매수 동향에 따른 상승 전망. 그러나 신용 물량 부담 및 과거 주가 하락 이력에 대한 부정적 의견 존재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['스페이스X', '기술력', '수혜주']</t>
+          <t>['실적', '외인환매수', '신용물량']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7380</v>
+        <v>1584</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.86%</t>
+          <t>'+0.70%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.05</v>
+        <v>-0.93</v>
       </c>
       <c r="E14" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F14" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="G14" t="n">
-        <v>305</v>
+        <v>232</v>
       </c>
       <c r="H14" t="n">
-        <v>25.45</v>
+        <v>0.84</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>7520</v>
+        <v>1573</v>
       </c>
       <c r="K14" t="n">
+        <v>1650</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1715</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1573</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="O14" t="n">
+        <v>29175665693</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2970</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>890</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-797000</v>
+      </c>
+      <c r="S14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="O14" t="n">
-        <v>11392000000</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>268000</v>
-      </c>
-      <c r="S14" t="n">
-        <v>-4000</v>
-      </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>실적 부진 및 유상증자 가능성에 대한 우려. 프로그램 환매수 관찰.</t>
+          <t>SpaceX 관련주로 부각되며 시간외 급등, 3분기 매출 161% 급증 소식에 대한 기대감. 그러나 개인 투자자들의 부정적인 언급과 프로그램 매도 물량이 관찰됨.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['실적', '유상증자', '환매수']</t>
+          <t>['SpaceX', '수혜주', '실적']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3100</v>
+        <v>3110</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.17%</t>
+          <t>'-3.86%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.73</v>
       </c>
       <c r="E15" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F15" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G15" t="n">
         <v>209</v>
@@ -1806,7 +1806,7 @@
         <v>0.73</v>
       </c>
       <c r="O15" t="n">
-        <v>10292441460</v>
+        <v>10465080142</v>
       </c>
       <c r="P15" t="n">
         <v>7050</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4265</v>
+        <v>4290</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-7.88%</t>
+          <t>'-7.34%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F16" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G16" t="n">
-        <v>542</v>
+        <v>562</v>
       </c>
       <c r="H16" t="n">
         <v>8.58</v>
@@ -1898,7 +1898,7 @@
         <v>8.57</v>
       </c>
       <c r="O16" t="n">
-        <v>21231509434</v>
+        <v>21629703699</v>
       </c>
       <c r="P16" t="n">
         <v>7560</v>
@@ -1907,14 +1907,14 @@
         <v>2930</v>
       </c>
       <c r="R16" t="n">
-        <v>-1377000</v>
+        <v>-1386000</v>
       </c>
       <c r="S16" t="n">
         <v>-462000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>낮은 PBR, 공매도 압박, 경영진 교체 요구 등 부정적 여론 형성. 주가 누르기 방지법 등 제도 개선 요구.</t>
+          <t>경영진 총사퇴, 주가 누르기 방지법 청원 등 부정적인 의견이 지배적. 공매도 및 프로그램 매도 물량 증가와 낮은 PBR에도 불구하고 주가 하락에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['PBR', '공매도', '경영진']</t>
+          <t>['공매도', '주가누르기', 'PBR']</t>
         </is>
       </c>
       <c r="X16" t="n">

--- a/data/trending_integrated_20261021_13.xlsx
+++ b/data/trending_integrated_20261021_13.xlsx
@@ -610,7 +610,7 @@
         <v>0.79</v>
       </c>
       <c r="O2" t="n">
-        <v>10584400257</v>
+        <v>10591315257</v>
       </c>
       <c r="P2" t="n">
         <v>2665</v>
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14850</v>
+        <v>14810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+22.93%</t>
+          <t>'+22.60%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -676,7 +676,7 @@
         <v>52</v>
       </c>
       <c r="G3" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0.27</v>
       </c>
       <c r="O3" t="n">
-        <v>92803032565</v>
+        <v>93990698285</v>
       </c>
       <c r="P3" t="n">
         <v>28800</v>
@@ -751,21 +751,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1828</v>
+        <v>1795</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+20.26%</t>
+          <t>'+18.09%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.12</v>
       </c>
       <c r="E4" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F4" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G4" t="n">
         <v>297</v>
@@ -794,7 +794,7 @@
         <v>0.57</v>
       </c>
       <c r="O4" t="n">
-        <v>58977454720</v>
+        <v>62170380520</v>
       </c>
       <c r="P4" t="n">
         <v>3980</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>그린하버의 경영권 인수 결정으로 인한 급등세. 355억 규모의 인수 발표와 역대급 거래량 터진 손바뀜에 대한 긍정적 전망. 인수설이 사실로 확인되며 급등.</t>
+          <t>푸드나무 경영권 인수설(그린하버 355억) 및 3연상 기대감. 초대형 호재 전 매집 목적 하한가 분석.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['인수', '경영권', '손바뀜']</t>
+          <t>['인수설', '경영권', '매집']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11110</v>
+        <v>11040</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.72%</t>
+          <t>'+13.00%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.4</v>
       </c>
       <c r="E5" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="F5" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G5" t="n">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="H5" t="n">
         <v>1.28</v>
@@ -886,7 +886,7 @@
         <v>0.88</v>
       </c>
       <c r="O5" t="n">
-        <v>268191049045</v>
+        <v>270675117280</v>
       </c>
       <c r="P5" t="n">
         <v>11690</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9280</v>
+        <v>9320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.28%</t>
+          <t>'+7.75%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.66</v>
       </c>
       <c r="E6" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F6" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G6" t="n">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="H6" t="n">
         <v>5.34</v>
@@ -978,7 +978,7 @@
         <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>29064706615</v>
+        <v>29316341575</v>
       </c>
       <c r="P6" t="n">
         <v>14940</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>나스닥 상장 철회 가능성 언급 및 테슬라 관련 긍정적 뉴스에 대한 기대감. 그러나 주가 상승 시 찔끔 오르는 모습과 개미 털기에 대한 부정적인 의견 존재.</t>
+          <t>명신산업의 미국 중복상장 시도 실패 및 국내 주가 관리 부재. 1만원대 안착 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['나스닥', '테슬라', '거래량']</t>
+          <t>['중복상장', '주가관리', '전망']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14810</v>
+        <v>221500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.59%</t>
+          <t>'+4.73%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>110</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>44</v>
+        <v>510</v>
       </c>
       <c r="G7" t="n">
-        <v>239</v>
+        <v>1769</v>
       </c>
       <c r="H7" t="n">
-        <v>9.82</v>
+        <v>46.08</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>14160</v>
+        <v>211500</v>
       </c>
       <c r="K7" t="n">
-        <v>14340</v>
+        <v>217000</v>
       </c>
       <c r="L7" t="n">
-        <v>14830</v>
+        <v>228000</v>
       </c>
       <c r="M7" t="n">
-        <v>14340</v>
+        <v>217000</v>
       </c>
       <c r="N7" t="n">
-        <v>9.779999999999999</v>
+        <v>46.04</v>
       </c>
       <c r="O7" t="n">
-        <v>26321431185</v>
+        <v>2590426095750</v>
       </c>
       <c r="P7" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>3320</v>
+        <v>94500</v>
       </c>
       <c r="R7" t="n">
-        <v>356000</v>
+        <v>2736000</v>
       </c>
       <c r="S7" t="n">
-        <v>14000</v>
+        <v>497000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>이재명 대통령 관련 언급과 함께 주가 조작 의혹 제기. 외인 보유율 유지 및 대차 해지 중요성 언급. 일부 긍정적 전망도 있으나, 전반적으로 부정적 여론 존재.</t>
+          <t>미국 중국 반도체 퇴출 결정, 외인 및 기관 동반 매수세 유입으로 인한 긍정적 전망. 그러나 개인 투자자들의 부정적 언급과 종가 음봉 마감에 대한 우려 존재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['주가조작', '외인보유율', '대차']</t>
+          <t>['반도체', '외인수급', '기관매수']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>221000</v>
+        <v>14790</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.49%</t>
+          <t>'+4.45%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>111</v>
       </c>
       <c r="F8" t="n">
-        <v>511</v>
+        <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>1780</v>
+        <v>243</v>
       </c>
       <c r="H8" t="n">
-        <v>46.08</v>
+        <v>9.82</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,47 +1147,47 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>211500</v>
+        <v>14160</v>
       </c>
       <c r="K8" t="n">
-        <v>217000</v>
+        <v>14340</v>
       </c>
       <c r="L8" t="n">
-        <v>228000</v>
+        <v>14830</v>
       </c>
       <c r="M8" t="n">
-        <v>217000</v>
+        <v>14340</v>
       </c>
       <c r="N8" t="n">
-        <v>46.04</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>2531679946000</v>
+        <v>27175528435</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q8" t="n">
-        <v>94500</v>
+        <v>3320</v>
       </c>
       <c r="R8" t="n">
-        <v>2736000</v>
+        <v>356000</v>
       </c>
       <c r="S8" t="n">
-        <v>497000</v>
+        <v>14000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 중국 반도체 퇴출 결정, 외인 및 기관 동반 매수세 유입으로 인한 긍정적 전망. 그러나 개인 투자자들의 부정적 언급과 종가 음봉 마감에 대한 우려 존재.</t>
+          <t>이재명 대통령 관련 언급과 함께 주가 조작 의혹 제기. 외인 보유율 유지 및 대차 해지 중요성 언급. 일부 긍정적 전망도 있으나, 전반적으로 부정적 여론 존재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['반도체', '외인수급', '기관매수']</t>
+          <t>['주가조작', '외인보유율', '대차']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,130 +1200,130 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>아주IB투자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2925</v>
+        <v>1271000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.99%</t>
+          <t>'+3.92%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.09</v>
+        <v>-0.04</v>
       </c>
       <c r="E9" t="n">
-        <v>76</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>33</v>
+        <v>489</v>
       </c>
       <c r="G9" t="n">
-        <v>231</v>
+        <v>1489</v>
       </c>
       <c r="H9" t="n">
-        <v>5.82</v>
+        <v>48.77</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>2840</v>
+        <v>1223000</v>
       </c>
       <c r="K9" t="n">
-        <v>3100</v>
+        <v>1260000</v>
       </c>
       <c r="L9" t="n">
-        <v>3300</v>
+        <v>1329000</v>
       </c>
       <c r="M9" t="n">
-        <v>2855</v>
+        <v>1254000</v>
       </c>
       <c r="N9" t="n">
-        <v>5.91</v>
+        <v>48.81</v>
       </c>
       <c r="O9" t="n">
-        <v>16681612989</v>
+        <v>3778295082500</v>
       </c>
       <c r="P9" t="n">
-        <v>19950</v>
+        <v>2987000</v>
       </c>
       <c r="Q9" t="n">
-        <v>1913</v>
+        <v>468000</v>
       </c>
       <c r="R9" t="n">
-        <v>-1060000</v>
+        <v>326000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>우주 섹터 관련 언급과 함께 주가 조작 의혹 제기. 반등 기대와 함께 신고 주장.</t>
+          <t>SK하이닉스의 지속적인 하락세와 단기 반등에 대한 불신. 솔리다임 상장 관련 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['우주섹터', '주가조작', '투자기업']</t>
+          <t>['하락세', '반등', '솔리다임']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>027360</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1259000</v>
+        <v>17810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.94%</t>
+          <t>'+2.83%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>94</v>
       </c>
       <c r="F10" t="n">
-        <v>481</v>
+        <v>53</v>
       </c>
       <c r="G10" t="n">
-        <v>1506</v>
+        <v>214</v>
       </c>
       <c r="H10" t="n">
-        <v>48.77</v>
+        <v>27.78</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1223000</v>
+        <v>17320</v>
       </c>
       <c r="K10" t="n">
-        <v>1260000</v>
+        <v>17480</v>
       </c>
       <c r="L10" t="n">
-        <v>1329000</v>
+        <v>17840</v>
       </c>
       <c r="M10" t="n">
-        <v>1254000</v>
+        <v>17170</v>
       </c>
       <c r="N10" t="n">
-        <v>48.81</v>
+        <v>27.78</v>
       </c>
       <c r="O10" t="n">
-        <v>3641889056000</v>
+        <v>36059054995</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>35350</v>
       </c>
       <c r="Q10" t="n">
-        <v>468000</v>
+        <v>17170</v>
       </c>
       <c r="R10" t="n">
-        <v>326000</v>
+        <v>488000</v>
       </c>
       <c r="S10" t="n">
-        <v>57000</v>
+        <v>13000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>개인 매도세와 연기금의 매도에 대한 부정적인 언급. 솔리다임 상장 관련 언급과 함께 주가 하락에 대한 불만 표출. 반등 시 기대감은 낮음.</t>
+          <t>조선, 방산, 원전 섹터 전반의 약세 속에서 주가 하락에 대한 부정적인 전망. 블랙록 매수 평균 단가 언급 등 일부 긍정적 요인도 있으나, 전반적으로 하락세 지속 우려.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['연기금', '개인매도', '솔리다임']</t>
+          <t>['조선', '방산', '원전']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,99 +1384,99 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>아주IB투자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17820</v>
+        <v>2905</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.89%</t>
+          <t>'+2.29%</t>
         </is>
       </c>
       <c r="D11" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="E11" t="n">
+        <v>77</v>
+      </c>
+      <c r="F11" t="n">
+        <v>34</v>
+      </c>
+      <c r="G11" t="n">
+        <v>252</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>2840</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3100</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3300</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2855</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="O11" t="n">
+        <v>16762553199</v>
+      </c>
+      <c r="P11" t="n">
+        <v>19950</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1913</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-1060000</v>
+      </c>
+      <c r="S11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="n">
-        <v>92</v>
-      </c>
-      <c r="F11" t="n">
-        <v>52</v>
-      </c>
-      <c r="G11" t="n">
-        <v>214</v>
-      </c>
-      <c r="H11" t="n">
-        <v>27.78</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>MarketType.KOSPI</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>17320</v>
-      </c>
-      <c r="K11" t="n">
-        <v>17480</v>
-      </c>
-      <c r="L11" t="n">
-        <v>17830</v>
-      </c>
-      <c r="M11" t="n">
-        <v>17170</v>
-      </c>
-      <c r="N11" t="n">
-        <v>27.78</v>
-      </c>
-      <c r="O11" t="n">
-        <v>35105208915</v>
-      </c>
-      <c r="P11" t="n">
-        <v>35350</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>17170</v>
-      </c>
-      <c r="R11" t="n">
-        <v>488000</v>
-      </c>
-      <c r="S11" t="n">
-        <v>13000</v>
-      </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>조선, 방산, 원전 섹터 전반의 약세 속에서 주가 하락에 대한 부정적인 전망. 블랙록 매수 평균 단가 언급 등 일부 긍정적 요인도 있으나, 전반적으로 하락세 지속 우려.</t>
+          <t>우주 섹터 관련 언급과 함께 주가 조작 의혹 제기. 반등 기대와 함께 신고 주장.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['조선', '방산', '원전']</t>
+          <t>['우주섹터', '주가조작', '투자기업']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>027360</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>64100</v>
+        <v>63900</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.07%</t>
+          <t>'+1.75%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F12" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G12" t="n">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="H12" t="n">
         <v>22.23</v>
@@ -1530,7 +1530,7 @@
         <v>22.29</v>
       </c>
       <c r="O12" t="n">
-        <v>68070195400</v>
+        <v>69196895450</v>
       </c>
       <c r="P12" t="n">
         <v>139200</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>원전 및 전력 관련주로 분류되나, 주가 부진 지속. 외국인 매도세 관찰.</t>
+          <t>두산에너빌리티의 원전 및 전력 관련 뉴스에도 불구하고 주가 부진. 연기금 매도 및 외인 매도 영향.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['원전', '전력', '외국인']</t>
+          <t>['원전', '주가부진', '연기금']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7400</v>
+        <v>7390</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.79%</t>
+          <t>'+1.65%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1596,7 +1596,7 @@
         <v>36</v>
       </c>
       <c r="G13" t="n">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="H13" t="n">
         <v>25.45</v>
@@ -1622,7 +1622,7 @@
         <v>25.4</v>
       </c>
       <c r="O13" t="n">
-        <v>11557760940</v>
+        <v>11827622400</v>
       </c>
       <c r="P13" t="n">
         <v>17950</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>3분기 실적 흑자 전환 기대감 및 외인 프로그램 환매수 동향에 따른 상승 전망. 그러나 신용 물량 부담 및 과거 주가 하락 이력에 대한 부정적 의견 존재.</t>
+          <t>LG디스플레이의 3분기 실적 기대감과 외국인 프로그램 매수세 유입 가능성. 2만원 직행 전망.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['실적', '외인환매수', '신용물량']</t>
+          <t>['실적', '외국인매수', '전망']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.70%</t>
+          <t>'+0.64%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.93</v>
       </c>
       <c r="E14" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F14" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G14" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H14" t="n">
         <v>0.84</v>
@@ -1714,7 +1714,7 @@
         <v>1.77</v>
       </c>
       <c r="O14" t="n">
-        <v>29175665693</v>
+        <v>29303177457</v>
       </c>
       <c r="P14" t="n">
         <v>2970</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3110</v>
+        <v>3090</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.86%</t>
+          <t>'-4.48%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.73</v>
       </c>
       <c r="E15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F15" t="n">
         <v>39</v>
       </c>
       <c r="G15" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1806,7 +1806,7 @@
         <v>0.73</v>
       </c>
       <c r="O15" t="n">
-        <v>10465080142</v>
+        <v>10534182707</v>
       </c>
       <c r="P15" t="n">
         <v>7050</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4290</v>
+        <v>4295</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-7.34%</t>
+          <t>'-7.24%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G16" t="n">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="H16" t="n">
         <v>8.58</v>
@@ -1898,7 +1898,7 @@
         <v>8.57</v>
       </c>
       <c r="O16" t="n">
-        <v>21629703699</v>
+        <v>21930593168</v>
       </c>
       <c r="P16" t="n">
         <v>7560</v>

--- a/data/trending_integrated_20261021_13.xlsx
+++ b/data/trending_integrated_20261021_13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:Z17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -610,7 +610,7 @@
         <v>0.79</v>
       </c>
       <c r="O2" t="n">
-        <v>10591315257</v>
+        <v>10592095257</v>
       </c>
       <c r="P2" t="n">
         <v>2665</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14810</v>
+        <v>14840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+22.60%</t>
+          <t>'+22.85%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.27</v>
       </c>
       <c r="E3" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F3" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G3" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0.27</v>
       </c>
       <c r="O3" t="n">
-        <v>93990698285</v>
+        <v>94930853530</v>
       </c>
       <c r="P3" t="n">
         <v>28800</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1795</v>
+        <v>1749</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+18.09%</t>
+          <t>'+15.07%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.12</v>
       </c>
       <c r="E4" t="n">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="F4" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G4" t="n">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="H4" t="n">
         <v>0.6899999999999999</v>
@@ -794,7 +794,7 @@
         <v>0.57</v>
       </c>
       <c r="O4" t="n">
-        <v>62170380520</v>
+        <v>64179883202</v>
       </c>
       <c r="P4" t="n">
         <v>3980</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>푸드나무 경영권 인수설(그린하버 355억) 및 3연상 기대감. 초대형 호재 전 매집 목적 하한가 분석.</t>
+          <t>그린하버의 푸드나무 인수 발표로 인한 경영권 프리미엄 기대감과 3연상 가능성에 대한 긍정적 전망이 지배적입니다.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['인수설', '경영권', '매집']</t>
+          <t>['인수', '경영권', '기대감']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11040</v>
+        <v>10920</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.00%</t>
+          <t>'+11.77%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.4</v>
       </c>
       <c r="E5" t="n">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="F5" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G5" t="n">
-        <v>447</v>
+        <v>464</v>
       </c>
       <c r="H5" t="n">
         <v>1.28</v>
@@ -886,7 +886,7 @@
         <v>0.88</v>
       </c>
       <c r="O5" t="n">
-        <v>270675117280</v>
+        <v>276725031380</v>
       </c>
       <c r="P5" t="n">
         <v>11690</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9320</v>
+        <v>9450</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.75%</t>
+          <t>'+9.25%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.66</v>
       </c>
       <c r="E6" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F6" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G6" t="n">
-        <v>320</v>
+        <v>339</v>
       </c>
       <c r="H6" t="n">
         <v>5.34</v>
@@ -978,7 +978,7 @@
         <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>29316341575</v>
+        <v>29957669695</v>
       </c>
       <c r="P6" t="n">
         <v>14940</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>명신산업의 미국 중복상장 시도 실패 및 국내 주가 관리 부재. 1만원대 안착 전망.</t>
+          <t>미국 상장 시도 실패 및 국내 주가 관리 부진에 대한 부정적 의견과, 1만원 안착 전망 등 엇갈리는 시각이 존재합니다.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1023,83 +1023,83 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>221500</v>
+        <v>13810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.73%</t>
+          <t>'+8.31%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>81</v>
       </c>
       <c r="F7" t="n">
-        <v>510</v>
+        <v>57</v>
       </c>
       <c r="G7" t="n">
-        <v>1769</v>
+        <v>488</v>
       </c>
       <c r="H7" t="n">
-        <v>46.08</v>
+        <v>3.15</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>211500</v>
+        <v>12750</v>
       </c>
       <c r="K7" t="n">
-        <v>217000</v>
+        <v>13080</v>
       </c>
       <c r="L7" t="n">
-        <v>228000</v>
+        <v>14290</v>
       </c>
       <c r="M7" t="n">
-        <v>217000</v>
+        <v>12680</v>
       </c>
       <c r="N7" t="n">
-        <v>46.04</v>
+        <v>3.15</v>
       </c>
       <c r="O7" t="n">
-        <v>2590426095750</v>
+        <v>119476214480</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q7" t="n">
-        <v>94500</v>
+        <v>1640</v>
       </c>
       <c r="R7" t="n">
-        <v>2736000</v>
+        <v>177000</v>
       </c>
       <c r="S7" t="n">
-        <v>497000</v>
+        <v>137000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 중국 반도체 퇴출 결정, 외인 및 기관 동반 매수세 유입으로 인한 긍정적 전망. 그러나 개인 투자자들의 부정적 언급과 종가 음봉 마감에 대한 우려 존재.</t>
+          <t>미국 AI 데이터센터향 광케이블 2차 물량 공급 개시 공시를 바탕으로 숏커버 및 2만원 이상 상승에 대한 기대감이 높습니다.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['반도체', '외인수급', '기관매수']</t>
+          <t>['광케이블', '공시', 'AI데이터센터']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14790</v>
+        <v>221250</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.45%</t>
+          <t>'+4.61%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>111</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>44</v>
+        <v>508</v>
       </c>
       <c r="G8" t="n">
-        <v>243</v>
+        <v>1789</v>
       </c>
       <c r="H8" t="n">
-        <v>9.82</v>
+        <v>46.08</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14160</v>
+        <v>211500</v>
       </c>
       <c r="K8" t="n">
-        <v>14340</v>
+        <v>217000</v>
       </c>
       <c r="L8" t="n">
-        <v>14830</v>
+        <v>228000</v>
       </c>
       <c r="M8" t="n">
-        <v>14340</v>
+        <v>217000</v>
       </c>
       <c r="N8" t="n">
-        <v>9.779999999999999</v>
+        <v>46.04</v>
       </c>
       <c r="O8" t="n">
-        <v>27175528435</v>
+        <v>2654999417500</v>
       </c>
       <c r="P8" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>3320</v>
+        <v>94500</v>
       </c>
       <c r="R8" t="n">
-        <v>356000</v>
+        <v>2736000</v>
       </c>
       <c r="S8" t="n">
-        <v>14000</v>
+        <v>497000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>이재명 대통령 관련 언급과 함께 주가 조작 의혹 제기. 외인 보유율 유지 및 대차 해지 중요성 언급. 일부 긍정적 전망도 있으나, 전반적으로 부정적 여론 존재.</t>
+          <t>외인 매수세 유입 및 긍정적 전망과 부정적 전망이 혼재된 가운데, 반도체 업황에 대한 기대감도 존재합니다.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['주가조작', '외인보유율', '대차']</t>
+          <t>['반도체', '외인수급', '전망']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1271000</v>
+        <v>14750</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.92%</t>
+          <t>'+4.17%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>115</v>
       </c>
       <c r="F9" t="n">
-        <v>489</v>
+        <v>45</v>
       </c>
       <c r="G9" t="n">
-        <v>1489</v>
+        <v>248</v>
       </c>
       <c r="H9" t="n">
-        <v>48.77</v>
+        <v>9.82</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,47 +1239,47 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1223000</v>
+        <v>14160</v>
       </c>
       <c r="K9" t="n">
-        <v>1260000</v>
+        <v>14340</v>
       </c>
       <c r="L9" t="n">
-        <v>1329000</v>
+        <v>14830</v>
       </c>
       <c r="M9" t="n">
-        <v>1254000</v>
+        <v>14340</v>
       </c>
       <c r="N9" t="n">
-        <v>48.81</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>3778295082500</v>
+        <v>27591136545</v>
       </c>
       <c r="P9" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q9" t="n">
-        <v>468000</v>
+        <v>3320</v>
       </c>
       <c r="R9" t="n">
-        <v>326000</v>
+        <v>356000</v>
       </c>
       <c r="S9" t="n">
-        <v>57000</v>
+        <v>14000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>SK하이닉스의 지속적인 하락세와 단기 반등에 대한 불신. 솔리다임 상장 관련 언급.</t>
+          <t>외국인 및 기관의 매수세 유입과 실적 우량주로서의 잠재력에 대한 긍정적 시각과 함께, 주가 조작 의혹 및 이재명 정부에 대한 비판이 존재합니다.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['하락세', '반등', '솔리다임']</t>
+          <t>['외인수급', '실적', '주가조작']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17810</v>
+        <v>1270000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.83%</t>
+          <t>'+3.84%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>94</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>53</v>
+        <v>489</v>
       </c>
       <c r="G10" t="n">
-        <v>214</v>
+        <v>1451</v>
       </c>
       <c r="H10" t="n">
-        <v>27.78</v>
+        <v>48.77</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>17320</v>
+        <v>1223000</v>
       </c>
       <c r="K10" t="n">
-        <v>17480</v>
+        <v>1260000</v>
       </c>
       <c r="L10" t="n">
-        <v>17840</v>
+        <v>1329000</v>
       </c>
       <c r="M10" t="n">
-        <v>17170</v>
+        <v>1254000</v>
       </c>
       <c r="N10" t="n">
-        <v>27.78</v>
+        <v>48.81</v>
       </c>
       <c r="O10" t="n">
-        <v>36059054995</v>
+        <v>3839715711500</v>
       </c>
       <c r="P10" t="n">
-        <v>35350</v>
+        <v>2987000</v>
       </c>
       <c r="Q10" t="n">
-        <v>17170</v>
+        <v>468000</v>
       </c>
       <c r="R10" t="n">
-        <v>488000</v>
+        <v>326000</v>
       </c>
       <c r="S10" t="n">
-        <v>13000</v>
+        <v>57000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>조선, 방산, 원전 섹터 전반의 약세 속에서 주가 하락에 대한 부정적인 전망. 블랙록 매수 평균 단가 언급 등 일부 긍정적 요인도 있으나, 전반적으로 하락세 지속 우려.</t>
+          <t>이재명 정부의 정책 실패와 주식 시장의 불안정성에 대한 불만이 팽배하며, 주가 하락에 대한 부정적 전망이 지배적입니다.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['조선', '방산', '원전']</t>
+          <t>['정책실패', '주가하락', '시장불안']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,169 +1384,169 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>아주IB투자</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2905</v>
+        <v>17770</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.29%</t>
+          <t>'+2.60%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="F11" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="G11" t="n">
-        <v>252</v>
+        <v>217</v>
       </c>
       <c r="H11" t="n">
-        <v>5.82</v>
+        <v>27.78</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>2840</v>
+        <v>17320</v>
       </c>
       <c r="K11" t="n">
-        <v>3100</v>
+        <v>17480</v>
       </c>
       <c r="L11" t="n">
-        <v>3300</v>
+        <v>17840</v>
       </c>
       <c r="M11" t="n">
-        <v>2855</v>
+        <v>17170</v>
       </c>
       <c r="N11" t="n">
-        <v>5.91</v>
+        <v>27.78</v>
       </c>
       <c r="O11" t="n">
-        <v>16762553199</v>
+        <v>37049437350</v>
       </c>
       <c r="P11" t="n">
-        <v>19950</v>
+        <v>35350</v>
       </c>
       <c r="Q11" t="n">
-        <v>1913</v>
+        <v>17170</v>
       </c>
       <c r="R11" t="n">
-        <v>-1060000</v>
+        <v>488000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>우주 섹터 관련 언급과 함께 주가 조작 의혹 제기. 반등 기대와 함께 신고 주장.</t>
+          <t>민주당 및 이재명 정부에 대한 비판과 함께 조선, 방산, 원전 섹터의 전반적인 부진 및 주가 하락에 대한 우려가 제기됩니다.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['우주섹터', '주가조작', '투자기업']</t>
+          <t>['정치비판', '섹터부진', '주가전망']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>027360</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>아주IB투자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>63900</v>
+        <v>2910</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.75%</t>
+          <t>'+2.46%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="E12" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="F12" t="n">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="G12" t="n">
-        <v>477</v>
+        <v>253</v>
       </c>
       <c r="H12" t="n">
-        <v>22.23</v>
+        <v>5.82</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>62800</v>
+        <v>2840</v>
       </c>
       <c r="K12" t="n">
-        <v>63600</v>
+        <v>3100</v>
       </c>
       <c r="L12" t="n">
-        <v>64800</v>
+        <v>3300</v>
       </c>
       <c r="M12" t="n">
-        <v>62600</v>
+        <v>2855</v>
       </c>
       <c r="N12" t="n">
-        <v>22.29</v>
+        <v>5.91</v>
       </c>
       <c r="O12" t="n">
-        <v>69196895450</v>
+        <v>16809556559</v>
       </c>
       <c r="P12" t="n">
-        <v>139200</v>
+        <v>19950</v>
       </c>
       <c r="Q12" t="n">
-        <v>57000</v>
+        <v>1913</v>
       </c>
       <c r="R12" t="n">
-        <v>-59000</v>
+        <v>-1060000</v>
       </c>
       <c r="S12" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>두산에너빌리티의 원전 및 전력 관련 뉴스에도 불구하고 주가 부진. 연기금 매도 및 외인 매도 영향.</t>
+          <t>공매도 세력에 대한 강한 비판과 주가 조작 의혹 제기, 그리고 외인 갭 띄우기 후 매도에 대한 불만이 팽배하며, 부정적 전망이 우세합니다.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['원전', '주가부진', '연기금']</t>
+          <t>['공매도', '주가조작', '외인']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>027360</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7390</v>
+        <v>7400</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.65%</t>
+          <t>'+1.79%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.05</v>
       </c>
       <c r="E13" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F13" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G13" t="n">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="H13" t="n">
         <v>25.45</v>
@@ -1622,7 +1622,7 @@
         <v>25.4</v>
       </c>
       <c r="O13" t="n">
-        <v>11827622400</v>
+        <v>11941644655</v>
       </c>
       <c r="P13" t="n">
         <v>17950</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>LG디스플레이의 3분기 실적 기대감과 외국인 프로그램 매수세 유입 가능성. 2만원 직행 전망.</t>
+          <t>외국인 매도세 및 개인 투자자들의 신용 문제, 그리고 실적 발표에 대한 불확실성이 혼재된 가운데, 부정적인 전망이 우세합니다.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['실적', '외국인매수', '전망']</t>
+          <t>['외인매도', '실적발표', '신용']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,31 +1667,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1583</v>
+        <v>63700</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.64%</t>
+          <t>'+1.43%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.93</v>
+        <v>-0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>85</v>
+        <v>152</v>
       </c>
       <c r="F14" t="n">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="G14" t="n">
-        <v>233</v>
+        <v>479</v>
       </c>
       <c r="H14" t="n">
-        <v>0.84</v>
+        <v>22.23</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1573</v>
+        <v>62800</v>
       </c>
       <c r="K14" t="n">
-        <v>1650</v>
+        <v>63600</v>
       </c>
       <c r="L14" t="n">
-        <v>1715</v>
+        <v>64800</v>
       </c>
       <c r="M14" t="n">
-        <v>1573</v>
+        <v>62600</v>
       </c>
       <c r="N14" t="n">
-        <v>1.77</v>
+        <v>22.29</v>
       </c>
       <c r="O14" t="n">
-        <v>29303177457</v>
+        <v>70454702000</v>
       </c>
       <c r="P14" t="n">
-        <v>2970</v>
+        <v>139200</v>
       </c>
       <c r="Q14" t="n">
-        <v>890</v>
+        <v>57000</v>
       </c>
       <c r="R14" t="n">
-        <v>-797000</v>
+        <v>-59000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>SpaceX 관련주로 부각되며 시간외 급등, 3분기 매출 161% 급증 소식에 대한 기대감. 그러나 개인 투자자들의 부정적인 언급과 프로그램 매도 물량이 관찰됨.</t>
+          <t>두산에너빌리티의 원전 및 전력 관련 뉴스에도 불구하고 주가 부진. 연기금 매도 및 외인 매도 영향.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['SpaceX', '수혜주', '실적']</t>
+          <t>['원전', '주가부진', '연기금']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,189 +1752,281 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>빅텍</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3090</v>
+        <v>1574</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.48%</t>
+          <t>'+0.06%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.73</v>
+        <v>-0.93</v>
       </c>
       <c r="E15" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F15" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="G15" t="n">
-        <v>210</v>
+        <v>238</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>3235</v>
+        <v>1573</v>
       </c>
       <c r="K15" t="n">
-        <v>3170</v>
+        <v>1650</v>
       </c>
       <c r="L15" t="n">
-        <v>3200</v>
+        <v>1715</v>
       </c>
       <c r="M15" t="n">
-        <v>3035</v>
+        <v>1573</v>
       </c>
       <c r="N15" t="n">
-        <v>0.73</v>
+        <v>1.77</v>
       </c>
       <c r="O15" t="n">
-        <v>10534182707</v>
+        <v>29594596952</v>
       </c>
       <c r="P15" t="n">
-        <v>7050</v>
+        <v>2970</v>
       </c>
       <c r="Q15" t="n">
-        <v>2500</v>
+        <v>890</v>
       </c>
       <c r="R15" t="n">
-        <v>-129000</v>
+        <v>-797000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>김정은 사망설 관련 북한발 뉴스로 인한 급락 및 투자자 불안 심리 고조. 공매도 언급.</t>
+          <t>SpaceX 관련주로 부각되며 시간외 급등, 3분기 매출 161% 급증 소식에 대한 기대감. 그러나 개인 투자자들의 부정적인 언급과 프로그램 매도 물량이 관찰됨.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['김정은 사망설', '북한 뉴스', '공매도']</t>
+          <t>['SpaceX', '수혜주', '실적']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>065450</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>한화생명</t>
+          <t>빅텍</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4295</v>
+        <v>3095</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-7.24%</t>
+          <t>'-4.33%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.01</v>
+        <v>-0.73</v>
       </c>
       <c r="E16" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="F16" t="n">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="G16" t="n">
-        <v>568</v>
+        <v>216</v>
       </c>
       <c r="H16" t="n">
-        <v>8.58</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>4630</v>
+        <v>3235</v>
       </c>
       <c r="K16" t="n">
-        <v>4645</v>
+        <v>3170</v>
       </c>
       <c r="L16" t="n">
-        <v>4645</v>
+        <v>3200</v>
       </c>
       <c r="M16" t="n">
-        <v>4240</v>
+        <v>3035</v>
       </c>
       <c r="N16" t="n">
-        <v>8.57</v>
+        <v>0.73</v>
       </c>
       <c r="O16" t="n">
-        <v>21930593168</v>
+        <v>10587394152</v>
       </c>
       <c r="P16" t="n">
-        <v>7560</v>
+        <v>7050</v>
       </c>
       <c r="Q16" t="n">
-        <v>2930</v>
+        <v>2500</v>
       </c>
       <c r="R16" t="n">
-        <v>-1386000</v>
+        <v>-129000</v>
       </c>
       <c r="S16" t="n">
-        <v>-462000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>경영진 총사퇴, 주가 누르기 방지법 청원 등 부정적인 의견이 지배적. 공매도 및 프로그램 매도 물량 증가와 낮은 PBR에도 불구하고 주가 하락에 대한 불만 표출.</t>
+          <t>김정은 사망설 관련 북한발 뉴스로 인한 급락 및 투자자 불안 심리 고조. 공매도 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>['김정은 사망설', '북한 뉴스', '공매도']</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>추적</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>065450</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>한화생명</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4277</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>'-7.62%</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E17" t="n">
+        <v>96</v>
+      </c>
+      <c r="F17" t="n">
+        <v>67</v>
+      </c>
+      <c r="G17" t="n">
+        <v>591</v>
+      </c>
+      <c r="H17" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>4630</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4645</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4645</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4240</v>
+      </c>
+      <c r="N17" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="O17" t="n">
+        <v>22186954111</v>
+      </c>
+      <c r="P17" t="n">
+        <v>7560</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2930</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-1386000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-462000</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>경영진 총사퇴, 주가 누르기 방지법 청원 등 부정적인 의견이 지배적. 공매도 및 프로그램 매도 물량 증가와 낮은 PBR에도 불구하고 주가 하락에 대한 불만 표출.</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
         <v>0.1</v>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>['공매도', '주가누르기', 'PBR']</t>
         </is>
       </c>
-      <c r="X16" t="n">
+      <c r="X17" t="n">
         <v>1</v>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>088350</t>
         </is>

--- a/data/trending_integrated_20261021_13.xlsx
+++ b/data/trending_integrated_20261021_13.xlsx
@@ -610,7 +610,7 @@
         <v>0.79</v>
       </c>
       <c r="O2" t="n">
-        <v>10592095257</v>
+        <v>10594275257</v>
       </c>
       <c r="P2" t="n">
         <v>2665</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14840</v>
+        <v>14820</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+22.85%</t>
+          <t>'+22.68%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.27</v>
       </c>
       <c r="E3" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F3" t="n">
         <v>53</v>
       </c>
       <c r="G3" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0.27</v>
       </c>
       <c r="O3" t="n">
-        <v>94930853530</v>
+        <v>95410549770</v>
       </c>
       <c r="P3" t="n">
         <v>28800</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1749</v>
+        <v>1758</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.07%</t>
+          <t>'+15.66%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.12</v>
       </c>
       <c r="E4" t="n">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="F4" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G4" t="n">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="H4" t="n">
         <v>0.6899999999999999</v>
@@ -794,7 +794,7 @@
         <v>0.57</v>
       </c>
       <c r="O4" t="n">
-        <v>64179883202</v>
+        <v>65517554633</v>
       </c>
       <c r="P4" t="n">
         <v>3980</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>그린하버의 푸드나무 인수 발표로 인한 경영권 프리미엄 기대감과 3연상 가능성에 대한 긍정적 전망이 지배적입니다.</t>
+          <t>푸드나무, 그린하버의 경영권 인수(주당 3500원) 공시 확인. 3연상 기대감 및 40% 이상 수익률 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['인수', '경영권', '기대감']</t>
+          <t>['인수', '경영권', '공시']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -854,13 +854,13 @@
         <v>0.4</v>
       </c>
       <c r="E5" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="F5" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G5" t="n">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="H5" t="n">
         <v>1.28</v>
@@ -886,7 +886,7 @@
         <v>0.88</v>
       </c>
       <c r="O5" t="n">
-        <v>276725031380</v>
+        <v>279553041255</v>
       </c>
       <c r="P5" t="n">
         <v>11690</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9450</v>
+        <v>9600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.25%</t>
+          <t>'+10.98%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.66</v>
       </c>
       <c r="E6" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="F6" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G6" t="n">
-        <v>339</v>
+        <v>387</v>
       </c>
       <c r="H6" t="n">
         <v>5.34</v>
@@ -969,7 +969,7 @@
         <v>9010</v>
       </c>
       <c r="L6" t="n">
-        <v>9610</v>
+        <v>9640</v>
       </c>
       <c r="M6" t="n">
         <v>8790</v>
@@ -978,7 +978,7 @@
         <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>29957669695</v>
+        <v>32202455310</v>
       </c>
       <c r="P6" t="n">
         <v>14940</v>
@@ -994,12 +994,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 상장 시도 실패 및 국내 주가 관리 부진에 대한 부정적 의견과, 1만원 안착 전망 등 엇갈리는 시각이 존재합니다.</t>
+          <t>명신산업, 미국 중복상장 시도 실패 및 국내 주가 관리 미흡 지적. 1만원대 안착 전망 제시.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13810</v>
+        <v>13780</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.31%</t>
+          <t>'+8.08%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G7" t="n">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="H7" t="n">
         <v>3.15</v>
@@ -1070,7 +1070,7 @@
         <v>3.15</v>
       </c>
       <c r="O7" t="n">
-        <v>119476214480</v>
+        <v>120338273040</v>
       </c>
       <c r="P7" t="n">
         <v>31500</v>
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="G8" t="n">
-        <v>1789</v>
+        <v>1764</v>
       </c>
       <c r="H8" t="n">
         <v>46.08</v>
@@ -1162,7 +1162,7 @@
         <v>46.04</v>
       </c>
       <c r="O8" t="n">
-        <v>2654999417500</v>
+        <v>2693995980750</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14750</v>
+        <v>1272000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.17%</t>
+          <t>'+4.01%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="E9" t="n">
-        <v>115</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>45</v>
+        <v>491</v>
       </c>
       <c r="G9" t="n">
-        <v>248</v>
+        <v>1491</v>
       </c>
       <c r="H9" t="n">
-        <v>9.82</v>
+        <v>48.77</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,47 +1239,47 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14160</v>
+        <v>1223000</v>
       </c>
       <c r="K9" t="n">
-        <v>14340</v>
+        <v>1260000</v>
       </c>
       <c r="L9" t="n">
-        <v>14830</v>
+        <v>1329000</v>
       </c>
       <c r="M9" t="n">
-        <v>14340</v>
+        <v>1254000</v>
       </c>
       <c r="N9" t="n">
-        <v>9.779999999999999</v>
+        <v>48.81</v>
       </c>
       <c r="O9" t="n">
-        <v>27591136545</v>
+        <v>3900119338500</v>
       </c>
       <c r="P9" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q9" t="n">
-        <v>3320</v>
+        <v>468000</v>
       </c>
       <c r="R9" t="n">
-        <v>356000</v>
+        <v>326000</v>
       </c>
       <c r="S9" t="n">
-        <v>14000</v>
+        <v>57000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>외국인 및 기관의 매수세 유입과 실적 우량주로서의 잠재력에 대한 긍정적 시각과 함께, 주가 조작 의혹 및 이재명 정부에 대한 비판이 존재합니다.</t>
+          <t>정치적 이슈와 연관된 부정적 언급 다수. 솔리다임 상장 관련 우려 제기.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['외인수급', '실적', '주가조작']</t>
+          <t>['솔리다임', '상장', '주주']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1270000</v>
+        <v>14690</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.84%</t>
+          <t>'+3.74%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>117</v>
       </c>
       <c r="F10" t="n">
-        <v>489</v>
+        <v>45</v>
       </c>
       <c r="G10" t="n">
-        <v>1451</v>
+        <v>250</v>
       </c>
       <c r="H10" t="n">
-        <v>48.77</v>
+        <v>9.82</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,47 +1331,47 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1223000</v>
+        <v>14160</v>
       </c>
       <c r="K10" t="n">
-        <v>1260000</v>
+        <v>14340</v>
       </c>
       <c r="L10" t="n">
-        <v>1329000</v>
+        <v>14830</v>
       </c>
       <c r="M10" t="n">
-        <v>1254000</v>
+        <v>14340</v>
       </c>
       <c r="N10" t="n">
-        <v>48.81</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>3839715711500</v>
+        <v>28181739050</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q10" t="n">
-        <v>468000</v>
+        <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>326000</v>
+        <v>356000</v>
       </c>
       <c r="S10" t="n">
-        <v>57000</v>
+        <v>14000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>이재명 정부의 정책 실패와 주식 시장의 불안정성에 대한 불만이 팽배하며, 주가 하락에 대한 부정적 전망이 지배적입니다.</t>
+          <t>외국인 및 기관의 매수세 유입과 실적 우량주로서의 잠재력에 대한 긍정적 시각과 함께, 주가 조작 의혹 및 이재명 정부에 대한 비판이 존재합니다.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['정책실패', '주가하락', '시장불안']</t>
+          <t>['외인수급', '실적', '주가조작']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17770</v>
+        <v>17760</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.60%</t>
+          <t>'+2.54%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1438,7 +1438,7 @@
         <v>27.78</v>
       </c>
       <c r="O11" t="n">
-        <v>37049437350</v>
+        <v>37675978315</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2910</v>
+        <v>2905</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.46%</t>
+          <t>'+2.29%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.09</v>
       </c>
       <c r="E12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G12" t="n">
         <v>253</v>
@@ -1530,7 +1530,7 @@
         <v>5.91</v>
       </c>
       <c r="O12" t="n">
-        <v>16809556559</v>
+        <v>16930360644</v>
       </c>
       <c r="P12" t="n">
         <v>19950</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7400</v>
+        <v>63800</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.79%</t>
+          <t>'+1.59%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="E13" t="n">
-        <v>86</v>
+        <v>155</v>
       </c>
       <c r="F13" t="n">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="G13" t="n">
-        <v>341</v>
+        <v>482</v>
       </c>
       <c r="H13" t="n">
-        <v>25.45</v>
+        <v>22.23</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>7270</v>
+        <v>62800</v>
       </c>
       <c r="K13" t="n">
-        <v>7360</v>
+        <v>63600</v>
       </c>
       <c r="L13" t="n">
-        <v>7520</v>
+        <v>64800</v>
       </c>
       <c r="M13" t="n">
-        <v>7250</v>
+        <v>62600</v>
       </c>
       <c r="N13" t="n">
-        <v>25.4</v>
+        <v>22.29</v>
       </c>
       <c r="O13" t="n">
-        <v>11941644655</v>
+        <v>71662504800</v>
       </c>
       <c r="P13" t="n">
-        <v>17950</v>
+        <v>139200</v>
       </c>
       <c r="Q13" t="n">
-        <v>7190</v>
+        <v>57000</v>
       </c>
       <c r="R13" t="n">
-        <v>268000</v>
+        <v>-59000</v>
       </c>
       <c r="S13" t="n">
-        <v>-4000</v>
+        <v>25000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>외국인 매도세 및 개인 투자자들의 신용 문제, 그리고 실적 발표에 대한 불확실성이 혼재된 가운데, 부정적인 전망이 우세합니다.</t>
+          <t>두산에너빌리티의 원전 및 전력 관련 뉴스에도 불구하고 주가 부진. 연기금 매도 및 외인 매도 영향.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['외인매도', '실적발표', '신용']</t>
+          <t>['원전', '주가부진', '연기금']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>63700</v>
+        <v>7380</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+1.43%</t>
+          <t>'+1.51%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E14" t="n">
-        <v>152</v>
+        <v>87</v>
       </c>
       <c r="F14" t="n">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="G14" t="n">
-        <v>479</v>
+        <v>343</v>
       </c>
       <c r="H14" t="n">
-        <v>22.23</v>
+        <v>25.45</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>62800</v>
+        <v>7270</v>
       </c>
       <c r="K14" t="n">
-        <v>63600</v>
+        <v>7360</v>
       </c>
       <c r="L14" t="n">
-        <v>64800</v>
+        <v>7520</v>
       </c>
       <c r="M14" t="n">
-        <v>62600</v>
+        <v>7250</v>
       </c>
       <c r="N14" t="n">
-        <v>22.29</v>
+        <v>25.4</v>
       </c>
       <c r="O14" t="n">
-        <v>70454702000</v>
+        <v>12168571575</v>
       </c>
       <c r="P14" t="n">
-        <v>139200</v>
+        <v>17950</v>
       </c>
       <c r="Q14" t="n">
-        <v>57000</v>
+        <v>7190</v>
       </c>
       <c r="R14" t="n">
-        <v>-59000</v>
+        <v>268000</v>
       </c>
       <c r="S14" t="n">
-        <v>25000</v>
+        <v>-4000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>두산에너빌리티의 원전 및 전력 관련 뉴스에도 불구하고 주가 부진. 연기금 매도 및 외인 매도 영향.</t>
+          <t>외국인 매도세 및 개인 투자자들의 신용 문제, 그리고 실적 발표에 대한 불확실성이 혼재된 가운데, 부정적인 전망이 우세합니다.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['원전', '주가부진', '연기금']</t>
+          <t>['외인매도', '실적발표', '신용']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1574</v>
+        <v>1565</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+0.06%</t>
+          <t>'-0.51%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.93</v>
       </c>
       <c r="E15" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F15" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G15" t="n">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="H15" t="n">
         <v>0.84</v>
@@ -1800,13 +1800,13 @@
         <v>1715</v>
       </c>
       <c r="M15" t="n">
-        <v>1573</v>
+        <v>1563</v>
       </c>
       <c r="N15" t="n">
         <v>1.77</v>
       </c>
       <c r="O15" t="n">
-        <v>29594596952</v>
+        <v>30074054045</v>
       </c>
       <c r="P15" t="n">
         <v>2970</v>
@@ -1866,13 +1866,13 @@
         <v>-0.73</v>
       </c>
       <c r="E16" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G16" t="n">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         <v>0.73</v>
       </c>
       <c r="O16" t="n">
-        <v>10587394152</v>
+        <v>10699566152</v>
       </c>
       <c r="P16" t="n">
         <v>7050</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>김정은 사망설 관련 북한발 뉴스로 인한 급락 및 투자자 불안 심리 고조. 공매도 언급.</t>
+          <t>김정은 사망설 관련 북한 동향 언급. 사망설 확산 시 주가 급등 가능성 제기.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['김정은 사망설', '북한 뉴스', '공매도']</t>
+          <t>['김정은', '사망설', '주가']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4277</v>
+        <v>4275</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-7.62%</t>
+          <t>'-7.67%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1964,7 +1964,7 @@
         <v>67</v>
       </c>
       <c r="G17" t="n">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="H17" t="n">
         <v>8.58</v>
@@ -1990,7 +1990,7 @@
         <v>8.57</v>
       </c>
       <c r="O17" t="n">
-        <v>22186954111</v>
+        <v>22508185785</v>
       </c>
       <c r="P17" t="n">
         <v>7560</v>
